--- a/Test Case/Test_Case.xlsx
+++ b/Test Case/Test_Case.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QA JOB\Test Case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757ED453-3332-43F9-B4E3-57657ACC014D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCED304-276A-4A69-B5CA-0A44ECD9F3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -500,7 +500,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -520,6 +520,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -530,19 +542,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -922,42 +921,42 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="30" style="20" customWidth="1"/>
+    <col min="3" max="3" width="30" style="14" customWidth="1"/>
     <col min="4" max="4" width="28.109375" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="30.5546875" style="20" customWidth="1"/>
+    <col min="6" max="6" width="30.5546875" style="14" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="25" style="20" customWidth="1"/>
+    <col min="11" max="11" width="25" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
       <c r="G3" t="s">
         <v>17</v>
       </c>
@@ -968,12 +967,12 @@
         <v>27</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
       <c r="G4" t="s">
         <v>23</v>
       </c>
@@ -984,12 +983,12 @@
         <v>1</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
       <c r="G5" t="s">
         <v>29</v>
       </c>
@@ -1000,12 +999,12 @@
         <v>2</v>
       </c>
       <c r="B6" s="1"/>
-      <c r="C6" s="14">
-        <v>46104</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
+      <c r="C6" s="18">
+        <v>46115</v>
+      </c>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
       <c r="G6" t="s">
         <v>30</v>
       </c>
@@ -1016,12 +1015,12 @@
         <v>3</v>
       </c>
       <c r="B7" s="1"/>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
       <c r="G7" t="s">
         <v>31</v>
       </c>
@@ -1032,12 +1031,12 @@
         <v>4</v>
       </c>
       <c r="B8" s="1"/>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
       <c r="G8" t="s">
         <v>32</v>
       </c>
@@ -1048,10 +1047,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="1"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
       <c r="G9" t="s">
         <v>18</v>
       </c>
@@ -1327,7 +1326,7 @@
       <c r="J18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K18" s="19"/>
+      <c r="K18" s="13"/>
     </row>
     <row r="19" spans="1:11" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
@@ -1360,7 +1359,7 @@
       <c r="J19" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K19" s="19"/>
+      <c r="K19" s="13"/>
     </row>
     <row r="20" spans="1:11" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
@@ -1393,7 +1392,7 @@
       <c r="J20" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K20" s="19"/>
+      <c r="K20" s="13"/>
     </row>
     <row r="21" spans="1:11" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
@@ -1426,7 +1425,7 @@
       <c r="J21" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K21" s="19"/>
+      <c r="K21" s="13"/>
     </row>
     <row r="22" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
@@ -1459,7 +1458,7 @@
       <c r="J22" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K22" s="19"/>
+      <c r="K22" s="13"/>
     </row>
     <row r="23" spans="1:11" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
@@ -1492,7 +1491,7 @@
       <c r="J23" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K23" s="19"/>
+      <c r="K23" s="13"/>
     </row>
     <row r="24" spans="1:11" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
@@ -1504,7 +1503,7 @@
       <c r="C24" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" t="s">
         <v>111</v>
       </c>
       <c r="E24" s="10" t="s">
@@ -1525,7 +1524,7 @@
       <c r="J24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="K24" s="19" t="s">
+      <c r="K24" s="13" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1560,7 +1559,7 @@
       <c r="J25" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K25" s="19"/>
+      <c r="K25" s="13"/>
     </row>
     <row r="26" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -1572,7 +1571,7 @@
       <c r="C26" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="12" t="s">
         <v>113</v>
       </c>
       <c r="E26" s="10" t="s">
@@ -1593,7 +1592,7 @@
       <c r="J26" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K26" s="19"/>
+      <c r="K26" s="13"/>
     </row>
     <row r="27" spans="1:11" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
@@ -1602,16 +1601,16 @@
       <c r="B27" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="16" t="s">
+      <c r="D27" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="13" t="s">
         <v>115</v>
       </c>
       <c r="G27" s="3" t="s">
@@ -1626,7 +1625,7 @@
       <c r="J27" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="K27" s="19"/>
+      <c r="K27" s="13"/>
     </row>
     <row r="28" spans="1:11" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
@@ -1644,7 +1643,7 @@
       <c r="E28" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="13" t="s">
         <v>107</v>
       </c>
       <c r="G28" s="3" t="s">
@@ -1659,13 +1658,13 @@
       <c r="J28" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K28" s="19"/>
+      <c r="K28" s="13"/>
     </row>
     <row r="29" spans="1:11" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="11" t="s">
         <v>116</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -1674,7 +1673,7 @@
       <c r="D29" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="11" t="s">
         <v>118</v>
       </c>
       <c r="F29" s="10" t="s">
@@ -1692,7 +1691,7 @@
       <c r="J29" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K29" s="19"/>
+      <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:11" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
@@ -1704,10 +1703,10 @@
       <c r="C30" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="16" t="s">
+      <c r="D30" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>123</v>
       </c>
       <c r="F30" s="10" t="s">
@@ -1725,197 +1724,197 @@
       <c r="J30" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K30" s="19"/>
+      <c r="K30" s="13"/>
     </row>
     <row r="31" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="K31" s="19"/>
+      <c r="C31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="K31" s="13"/>
     </row>
     <row r="32" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="K32" s="19"/>
+      <c r="C32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="K32" s="13"/>
     </row>
     <row r="33" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="K33" s="19"/>
+      <c r="C33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="K33" s="13"/>
     </row>
     <row r="34" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="K34" s="19"/>
+      <c r="C34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="K34" s="13"/>
     </row>
     <row r="35" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="K35" s="19"/>
+      <c r="C35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="K35" s="13"/>
     </row>
     <row r="36" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="K36" s="19"/>
+      <c r="C36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="K36" s="13"/>
     </row>
     <row r="37" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="K37" s="19"/>
+      <c r="C37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="K37" s="13"/>
     </row>
     <row r="38" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="K38" s="19"/>
+      <c r="C38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="K38" s="13"/>
     </row>
     <row r="39" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="K39" s="19"/>
+      <c r="C39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="K39" s="13"/>
     </row>
     <row r="40" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="K40" s="19"/>
+      <c r="C40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="K40" s="13"/>
     </row>
     <row r="41" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="K41" s="19"/>
+      <c r="C41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="K41" s="13"/>
     </row>
     <row r="42" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="K42" s="19"/>
+      <c r="C42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="K42" s="13"/>
     </row>
     <row r="43" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="K43" s="19"/>
+      <c r="C43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="K43" s="13"/>
     </row>
     <row r="44" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="K44" s="19"/>
+      <c r="C44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="K44" s="13"/>
     </row>
     <row r="45" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="K45" s="19"/>
+      <c r="C45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="K45" s="13"/>
     </row>
     <row r="46" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="K46" s="19"/>
+      <c r="C46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="K46" s="13"/>
     </row>
     <row r="47" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="K47" s="19"/>
+      <c r="C47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="K47" s="13"/>
     </row>
     <row r="48" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="K48" s="19"/>
+      <c r="C48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="K48" s="13"/>
     </row>
     <row r="49" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="K49" s="19"/>
+      <c r="C49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="K49" s="13"/>
     </row>
     <row r="50" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="K50" s="19"/>
+      <c r="C50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="K50" s="13"/>
     </row>
     <row r="51" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="K51" s="19"/>
+      <c r="C51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="K51" s="13"/>
     </row>
     <row r="52" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="K52" s="19"/>
+      <c r="C52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="K52" s="13"/>
     </row>
     <row r="53" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="K53" s="19"/>
+      <c r="C53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="K53" s="13"/>
     </row>
     <row r="54" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="K54" s="19"/>
+      <c r="C54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="K54" s="13"/>
     </row>
     <row r="55" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="K55" s="19"/>
+      <c r="C55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="K55" s="13"/>
     </row>
     <row r="56" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="K56" s="19"/>
+      <c r="C56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="K56" s="13"/>
     </row>
     <row r="57" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="K57" s="19"/>
+      <c r="C57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="K57" s="13"/>
     </row>
     <row r="58" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C58" s="19"/>
-      <c r="F58" s="19"/>
-      <c r="K58" s="19"/>
+      <c r="C58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="K58" s="13"/>
     </row>
     <row r="59" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="K59" s="19"/>
+      <c r="C59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="K59" s="13"/>
     </row>
     <row r="60" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="K60" s="19"/>
+      <c r="C60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="K60" s="13"/>
     </row>
     <row r="61" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="K61" s="19"/>
+      <c r="C61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="K61" s="13"/>
     </row>
     <row r="62" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="K62" s="19"/>
+      <c r="C62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="K62" s="13"/>
     </row>
     <row r="63" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="K63" s="19"/>
+      <c r="C63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="K63" s="13"/>
     </row>
     <row r="64" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="K64" s="19"/>
+      <c r="C64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="K64" s="13"/>
     </row>
     <row r="65" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="K65" s="19"/>
+      <c r="C65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="K65" s="13"/>
     </row>
     <row r="66" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="K66" s="19"/>
+      <c r="C66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="K66" s="13"/>
     </row>
     <row r="67" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="19"/>
-      <c r="F67" s="19"/>
-      <c r="K67" s="19"/>
+      <c r="C67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="K67" s="13"/>
     </row>
     <row r="68" spans="3:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="19"/>
-      <c r="F68" s="19"/>
-      <c r="K68" s="19"/>
+      <c r="C68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="K68" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="8">
